--- a/mistral_translate_work/split_by_prompt/excel/ui/lang_multi_text/lang_multi_text__ui__part_0008.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/ui/lang_multi_text/lang_multi_text__ui__part_0008.xlsx
@@ -1029,7 +1029,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Refresh</t>
+          <t>Làm mới</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Resonance Skill</t>
+          <t>Resonator Skill</t>
         </is>
       </c>
     </row>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Xác nhận để bắt đầu với Resonator đã chọn và Weapon mặc định?</t>
+          <t>Xác nhận để bắt đầu với Resonator đã chọn và Vũ khí mặc định?</t>
         </is>
       </c>
     </row>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Exit</t>
+          <t>Thoát</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Stats</t>
+          <t>Chỉ số</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Tất cả Hình thức Weapon</t>
+          <t>Tất cả Hình thức Vũ khí</t>
         </is>
       </c>
     </row>
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Stats Nâng cấp Weapon</t>
+          <t>Stats Nâng cấp Vũ khí</t>
         </is>
       </c>
     </row>
@@ -5449,7 +5449,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=press Gamepad=Touch} bất cứ đâu để đóng</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Tap} bất cứ đâu để đóng</t>
         </is>
       </c>
     </row>
@@ -6359,7 +6359,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Warehouse</t>
+          <t>Kho</t>
         </is>
       </c>
     </row>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Warehouse</t>
+          <t>Kho</t>
         </is>
       </c>
     </row>
@@ -7269,7 +7269,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Warehouse</t>
+          <t>Kho</t>
         </is>
       </c>
     </row>
@@ -9349,7 +9349,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Shop</t>
+          <t>Cửa hàng</t>
         </is>
       </c>
     </row>
@@ -10779,7 +10779,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Touch PC=click Gamepad=press}</t>
+          <t>{Cus:Ipt,Touch=Tap PC=Click Gamepad=Press}</t>
         </is>
       </c>
     </row>
@@ -10909,7 +10909,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Warehouse</t>
+          <t>Kho</t>
         </is>
       </c>
     </row>
@@ -10974,7 +10974,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Warehouse</t>
+          <t>Kho</t>
         </is>
       </c>
     </row>
@@ -14289,7 +14289,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Đã hoàn thành</t>
         </is>
       </c>
     </row>
@@ -14484,7 +14484,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Exchange Service Credit</t>
+          <t>Trao Đổi Credit Dịch Vụ</t>
         </is>
       </c>
     </row>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Exchange Service Credit</t>
+          <t>Trao Đổi Credit Dịch Vụ</t>
         </is>
       </c>
     </row>
@@ -21959,7 +21959,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Return</t>
+          <t>Trở về</t>
         </is>
       </c>
     </row>
@@ -22024,7 +22024,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Bắt đầu lại</t>
         </is>
       </c>
     </row>
@@ -23389,7 +23389,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Đã hoàn thành</t>
         </is>
       </c>
     </row>
@@ -23844,7 +23844,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Owned</t>
+          <t>Đã sở hữu</t>
         </is>
       </c>
     </row>
@@ -25339,7 +25339,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Pioneer Association</t>
+          <t>Hiệp Hội Tiên Phong</t>
         </is>
       </c>
     </row>
@@ -25664,7 +25664,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Send</t>
+          <t>Gửi</t>
         </is>
       </c>
     </row>
@@ -25729,7 +25729,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Send</t>
+          <t>Gửi</t>
         </is>
       </c>
     </row>
@@ -25859,7 +25859,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Chạm vào bất kỳ đâu PC=Nhấp bất kỳ đâu Gamepad=Nhấn bất kỳ nút nào} để đóng</t>
+          <t>{Cus:Ipt,Touch=Tap anywhere PC=Click anywhere Gamepad=Press any button} để đóng</t>
         </is>
       </c>
     </row>
@@ -27289,7 +27289,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Bắt đầu lại</t>
         </is>
       </c>
     </row>
@@ -27939,7 +27939,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Return</t>
+          <t>Trở về</t>
         </is>
       </c>
     </row>
@@ -28134,7 +28134,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Chạm vào bất kỳ đâu PC=Nhấp bất kỳ đâu Gamepad=Nhấn bất kỳ nút nào} để đóng</t>
+          <t>{Cus:Ipt,Touch=Tap anywhere PC=Click anywhere Gamepad=Press any button} để đóng</t>
         </is>
       </c>
     </row>
@@ -28199,7 +28199,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=Chạm vào bất kỳ đâu PC=Nhấp bất kỳ đâu Gamepad=Nhấn bất kỳ nút nào} để đóng</t>
+          <t>{Cus:Ipt,Touch=Tap anywhere PC=Click anywhere Gamepad=Press any button} để đóng</t>
         </is>
       </c>
     </row>
@@ -31774,7 +31774,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Đã hoàn thành</t>
         </is>
       </c>
     </row>
